--- a/apps/api/data/excel_templates/cities.xlsx
+++ b/apps/api/data/excel_templates/cities.xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787792A2-1B2C-3549-822B-F3899B6C1A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8195D9-B945-F24E-9B45-39F506DDB995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cities" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cities!$A$1:$Y$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cities!$A$1:$Z$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="1358">
   <si>
     <t>name</t>
   </si>
@@ -3542,9 +3543,6 @@
     <t>Friendly, eco-aware, innovative, community-oriented</t>
   </si>
   <si>
-    <t>Danish (official), English, German, Arabic</t>
-  </si>
-  <si>
     <t>Aalborg University</t>
   </si>
   <si>
@@ -3578,9 +3576,6 @@
     <t>Knowledgeable, multicultural, eco-conscious, innovative</t>
   </si>
   <si>
-    <t>German (official), English, Turkish, Arabic</t>
-  </si>
-  <si>
     <t>RWTH Aachen University, FH Aachen University of Applied Sciences</t>
   </si>
   <si>
@@ -3614,9 +3609,6 @@
     <t>Ambitious, young, growing rapidly, urbanized</t>
   </si>
   <si>
-    <t>Arabic (official), English, French</t>
-  </si>
-  <si>
     <t>October 6 University, Misr University for Science and Technology, Nile University</t>
   </si>
   <si>
@@ -4137,15 +4129,23 @@
   </si>
   <si>
     <t>6th of October City</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>German, English, Turkish, Arabic</t>
+  </si>
+  <si>
+    <t>Danish, English, German, Arabic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="165" formatCode="[$€-2]\ #,##0;[Red]\-[$€-2]\ #,##0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0000000000"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -4206,24 +4206,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4577,27 +4578,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA102"/>
+  <dimension ref="A1:AB102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="21" customWidth="1"/>
-    <col min="13" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="26" customWidth="1"/>
-    <col min="19" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="27" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="22" customWidth="1"/>
-    <col min="23" max="25" width="18" customWidth="1"/>
+    <col min="9" max="9" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="18" style="7" customWidth="1"/>
+    <col min="12" max="12" width="21" style="7" customWidth="1"/>
+    <col min="13" max="13" width="18" style="7" customWidth="1"/>
+    <col min="14" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="26" style="7" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="27" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="69" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="18" style="9" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4626,63 +4630,66 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="16">
+    <row r="2" spans="1:28" ht="16">
       <c r="A2" s="2" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>794</v>
@@ -4691,157 +4698,157 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>1189</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="S2" s="6">
+        <v>15</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3" t="s">
         <v>1195</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>1194</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="R2" s="2">
-        <v>15</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6" t="s">
-        <v>1198</v>
-      </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:28">
       <c r="A3" s="2" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G3" s="2">
         <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="J3" s="4">
+        <v>1179</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="6">
         <v>45000</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="6">
+        <v>320000</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="4">
-        <v>320000</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>1179</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="R3" s="2">
+        <v>1176</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="S3" s="6">
         <v>4</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>1176</v>
-      </c>
       <c r="T3" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>1175</v>
-      </c>
       <c r="V3" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2" t="s">
-        <v>1197</v>
+        <v>1356</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2" t="s">
+        <v>1194</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="16">
+    <row r="4" spans="1:28" ht="16">
       <c r="A4" s="2" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G4" s="2">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J4" s="4">
+        <v>1169</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="6">
         <v>55000</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="6">
+        <v>310000</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="L4" s="4">
-        <v>310000</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>1169</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>1168</v>
@@ -4852,35 +4859,38 @@
       <c r="Q4" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="S4" s="6">
         <v>3</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>1165</v>
-      </c>
       <c r="T4" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="2" t="s">
-        <v>1164</v>
-      </c>
       <c r="V4" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2" t="s">
-        <v>1183</v>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2" t="s">
+        <v>1181</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="16">
+    <row r="5" spans="1:28" ht="16">
       <c r="A5" s="2" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1151</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>1161</v>
@@ -4894,59 +4904,60 @@
       <c r="I5" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="2"/>
+      <c r="K5" s="6">
         <v>48000</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="6">
+        <v>290000</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="4">
-        <v>290000</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="6">
         <v>6</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2" t="s">
-        <v>1172</v>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2" t="s">
+        <v>1171</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="16">
+    <row r="6" spans="1:28" ht="16">
       <c r="A6" s="2" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>1136</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>1150</v>
@@ -4960,59 +4971,60 @@
       <c r="I6" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2"/>
+      <c r="K6" s="5" t="s">
         <v>1146</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="6">
         <v>3</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2" t="s">
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:28">
       <c r="A7" s="2" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>1126</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>1135</v>
@@ -5026,59 +5038,60 @@
       <c r="I7" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="2"/>
+      <c r="K7" s="6">
         <v>58000</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="6">
+        <v>370000</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L7" s="4">
-        <v>370000</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="6">
         <v>8</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2" t="s">
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="16">
+    <row r="8" spans="1:28" ht="16">
       <c r="A8" s="2" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>1125</v>
@@ -5092,59 +5105,60 @@
       <c r="I8" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2"/>
+      <c r="K8" s="5" t="s">
         <v>1121</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="6">
         <v>2</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2" t="s">
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:28">
       <c r="A9" s="2" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>1114</v>
@@ -5158,59 +5172,60 @@
       <c r="I9" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="2"/>
+      <c r="K9" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="6">
         <v>3</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2" t="s">
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="16">
+    <row r="10" spans="1:28" ht="16">
       <c r="A10" s="2" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1087</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>1102</v>
@@ -5224,59 +5239,60 @@
       <c r="I10" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2"/>
+      <c r="K10" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="6">
         <v>4</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="U10" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2" t="s">
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:28">
       <c r="A11" s="2" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>1071</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>1086</v>
@@ -5290,59 +5306,60 @@
       <c r="I11" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="2"/>
+      <c r="K11" s="6" t="s">
         <v>1082</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="6">
         <v>4</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="U11" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2" t="s">
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="16">
+    <row r="12" spans="1:28" ht="16">
       <c r="A12" s="2" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>1059</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>1070</v>
@@ -5356,59 +5373,60 @@
       <c r="I12" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="2"/>
+      <c r="K12" s="5" t="s">
         <v>1066</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="R12" s="2">
+      <c r="S12" s="6">
         <v>2</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="U12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2" t="s">
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2" t="s">
         <v>1085</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="16">
+    <row r="13" spans="1:28" ht="16">
       <c r="A13" s="2" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>1047</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>1058</v>
@@ -5422,59 +5440,60 @@
       <c r="I13" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="2"/>
+      <c r="K13" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="R13" s="2">
+      <c r="S13" s="6">
         <v>4</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="U13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="W13" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2" t="s">
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="16">
+    <row r="14" spans="1:28" ht="16">
       <c r="A14" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1036</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>1046</v>
@@ -5488,59 +5507,60 @@
       <c r="I14" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="2"/>
+      <c r="K14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="R14" s="2">
+      <c r="S14" s="6">
         <v>3</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="U14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="V14" s="2" t="s">
+      <c r="W14" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2" t="s">
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="16">
+    <row r="15" spans="1:28" ht="16">
       <c r="A15" s="2" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1026</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>1035</v>
@@ -5554,59 +5574,60 @@
       <c r="I15" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="2"/>
+      <c r="K15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="R15" s="2">
+      <c r="S15" s="6">
         <v>6</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="U15" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="W15" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2" t="s">
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:28">
       <c r="A16" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>1025</v>
@@ -5620,59 +5641,60 @@
       <c r="I16" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="2"/>
+      <c r="K16" s="6" t="s">
         <v>1021</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="R16" s="2">
+      <c r="S16" s="6">
         <v>4</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="U16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="V16" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="V16" s="2" t="s">
+      <c r="W16" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2" t="s">
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="16">
+    <row r="17" spans="1:28" ht="16">
       <c r="A17" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1003</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>1012</v>
@@ -5686,59 +5708,60 @@
       <c r="I17" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="2"/>
+      <c r="K17" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="R17" s="2">
+      <c r="S17" s="6">
         <v>2</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="U17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="V17" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="W17" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2" t="s">
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="16">
+    <row r="18" spans="1:28" ht="16">
       <c r="A18" s="2" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>993</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>1002</v>
@@ -5752,59 +5775,60 @@
       <c r="I18" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="2"/>
+      <c r="K18" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="R18" s="2">
+      <c r="S18" s="6">
         <v>1</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="U18" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V18" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2" t="s">
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:28">
       <c r="A19" s="2" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>981</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>992</v>
@@ -5818,59 +5842,60 @@
       <c r="I19" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="2"/>
+      <c r="K19" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>988</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="R19" s="2">
+      <c r="S19" s="6">
         <v>5</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="U19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="V19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V19" s="2" t="s">
+      <c r="W19" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2" t="s">
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="16">
+    <row r="20" spans="1:28" ht="16">
       <c r="A20" s="2" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>970</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>980</v>
@@ -5884,59 +5909,60 @@
       <c r="I20" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="2"/>
+      <c r="K20" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R20" s="2">
+      <c r="S20" s="6">
         <v>10</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="U20" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="V20" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="V20" s="2" t="s">
+      <c r="W20" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2" t="s">
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="16">
+    <row r="21" spans="1:28" ht="16">
       <c r="A21" s="2" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>959</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>969</v>
@@ -5950,59 +5976,60 @@
       <c r="I21" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="2"/>
+      <c r="K21" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="N21" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="R21" s="2">
+      <c r="S21" s="6">
         <v>2</v>
       </c>
-      <c r="S21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="T21" s="2" t="s">
+      <c r="U21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="V21" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="V21" s="2" t="s">
+      <c r="W21" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2" t="s">
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="16">
+    <row r="22" spans="1:28" ht="16">
       <c r="A22" s="2" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>947</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>958</v>
@@ -6016,59 +6043,60 @@
       <c r="I22" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="2"/>
+      <c r="K22" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="L22" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N22" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="R22" s="2">
+      <c r="S22" s="6">
         <v>1</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="U22" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="V22" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="V22" s="2" t="s">
+      <c r="W22" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2" t="s">
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:28">
       <c r="A23" s="2" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>937</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>946</v>
@@ -6082,59 +6110,60 @@
       <c r="I23" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="2"/>
+      <c r="K23" s="6">
         <v>30000</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="6">
+        <v>420000</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L23" s="4">
-        <v>420000</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="R23" s="2">
+      <c r="S23" s="6">
         <v>3</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="U23" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="W23" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2" t="s">
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="16">
+    <row r="24" spans="1:28" ht="16">
       <c r="A24" s="2" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>926</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>936</v>
@@ -6148,59 +6177,60 @@
       <c r="I24" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="2"/>
+      <c r="K24" s="6">
         <v>28000</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="6">
+        <v>310000</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L24" s="4">
-        <v>310000</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="R24" s="2">
+      <c r="S24" s="6">
         <v>2</v>
       </c>
-      <c r="S24" s="2" t="s">
+      <c r="T24" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="U24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="V24" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="V24" s="2" t="s">
+      <c r="W24" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2" t="s">
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:28">
       <c r="A25" s="2" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>911</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>925</v>
@@ -6214,59 +6244,60 @@
       <c r="I25" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="2"/>
+      <c r="K25" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="L25" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="N25" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="R25" s="2">
+      <c r="S25" s="6">
         <v>4</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="T25" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="T25" s="2" t="s">
+      <c r="U25" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="U25" s="2" t="s">
+      <c r="V25" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="V25" s="2" t="s">
+      <c r="W25" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2" t="s">
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="16">
+    <row r="26" spans="1:28" ht="16">
       <c r="A26" s="2" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>900</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>910</v>
@@ -6280,59 +6311,60 @@
       <c r="I26" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="2"/>
+      <c r="K26" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="N26" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="R26" s="2">
+      <c r="S26" s="6">
         <v>1</v>
       </c>
-      <c r="S26" s="2" t="s">
+      <c r="T26" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="T26" s="2" t="s">
+      <c r="U26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U26" s="2" t="s">
+      <c r="V26" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V26" s="2" t="s">
+      <c r="W26" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2" t="s">
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="16">
+    <row r="27" spans="1:28" ht="16">
       <c r="A27" s="2" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>889</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>899</v>
@@ -6346,59 +6378,60 @@
       <c r="I27" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="2"/>
+      <c r="K27" s="5" t="s">
         <v>894</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="L27" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="R27" s="2">
+      <c r="S27" s="6">
         <v>3</v>
       </c>
-      <c r="S27" s="2" t="s">
+      <c r="T27" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="T27" s="2" t="s">
+      <c r="U27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="V27" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V27" s="2" t="s">
+      <c r="W27" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2" t="s">
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:28">
       <c r="A28" s="2" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>876</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>888</v>
@@ -6412,59 +6445,60 @@
       <c r="I28" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="2"/>
+      <c r="K28" s="6" t="s">
         <v>884</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="N28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="N28" s="2" t="s">
+      <c r="O28" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R28" s="2">
+      <c r="S28" s="6">
         <v>2</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="T28" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="T28" s="2" t="s">
+      <c r="U28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="V28" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="V28" s="2" t="s">
+      <c r="W28" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2" t="s">
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="16">
+    <row r="29" spans="1:28" ht="16">
       <c r="A29" s="2" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>866</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>875</v>
@@ -6478,59 +6512,60 @@
       <c r="I29" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="2"/>
+      <c r="K29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="R29" s="2">
+      <c r="S29" s="6">
         <v>4</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="T29" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="T29" s="2" t="s">
+      <c r="U29" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="V29" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="V29" s="2" t="s">
+      <c r="W29" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2" t="s">
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:28">
       <c r="A30" s="2" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>856</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>865</v>
@@ -6544,59 +6579,60 @@
       <c r="I30" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="2"/>
+      <c r="K30" s="6">
         <v>6500</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="6">
+        <v>50000</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="N30" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L30" s="4">
-        <v>50000</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="R30" s="2">
+      <c r="S30" s="6">
         <v>2</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="T30" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="T30" s="2" t="s">
+      <c r="U30" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="V30" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="V30" s="2" t="s">
+      <c r="W30" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="Z30" s="2"/>
-      <c r="AA30" s="2" t="s">
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="16">
+    <row r="31" spans="1:28" ht="16">
       <c r="A31" s="2" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>846</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>855</v>
@@ -6610,59 +6646,60 @@
       <c r="I31" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="2"/>
+      <c r="K31" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="L31" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="R31" s="2">
+      <c r="S31" s="6">
         <v>1</v>
       </c>
-      <c r="S31" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="T31" s="2" t="s">
+      <c r="U31" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="V31" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="V31" s="2" t="s">
+      <c r="W31" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="Z31" s="2"/>
-      <c r="AA31" s="2" t="s">
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="16">
+    <row r="32" spans="1:28" ht="16">
       <c r="A32" s="2" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>834</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>845</v>
@@ -6676,59 +6713,60 @@
       <c r="I32" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="2"/>
+      <c r="K32" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="N32" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="Q32" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="R32" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="R32" s="2">
+      <c r="S32" s="6">
         <v>2</v>
       </c>
-      <c r="S32" s="2" t="s">
+      <c r="T32" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="U32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="V32" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="V32" s="2" t="s">
+      <c r="W32" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2" t="s">
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:28">
       <c r="A33" s="2" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>823</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>833</v>
@@ -6742,59 +6780,60 @@
       <c r="I33" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="J33" s="4">
+      <c r="J33" s="2"/>
+      <c r="K33" s="6">
         <v>40000</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N33" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L33" s="4">
-        <v>400000</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="N33" s="2" t="s">
+      <c r="O33" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="Q33" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="R33" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="R33" s="2">
+      <c r="S33" s="6">
         <v>3</v>
       </c>
-      <c r="S33" s="2" t="s">
+      <c r="T33" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="U33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="V33" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="V33" s="2" t="s">
+      <c r="W33" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="Z33" s="2"/>
-      <c r="AA33" s="2" t="s">
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="16">
+    <row r="34" spans="1:28" ht="16">
       <c r="A34" s="2" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>815</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>822</v>
@@ -6808,59 +6847,60 @@
       <c r="I34" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="2"/>
+      <c r="K34" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="L34" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="Q34" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="R34" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="R34" s="2">
+      <c r="S34" s="6">
         <v>2</v>
       </c>
-      <c r="S34" s="2" t="s">
+      <c r="T34" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="U34" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U34" s="2" t="s">
+      <c r="V34" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V34" s="2" t="s">
+      <c r="W34" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2" t="s">
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="16">
+    <row r="35" spans="1:28" ht="16">
       <c r="A35" s="2" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>804</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>814</v>
@@ -6874,59 +6914,60 @@
       <c r="I35" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="2"/>
+      <c r="K35" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="L35" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="Q35" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="R35" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="R35" s="2">
+      <c r="S35" s="6">
         <v>5</v>
       </c>
-      <c r="S35" s="2" t="s">
+      <c r="T35" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="T35" s="2" t="s">
+      <c r="U35" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="U35" s="2" t="s">
+      <c r="V35" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V35" s="2" t="s">
+      <c r="W35" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="Z35" s="2"/>
-      <c r="AA35" s="2" t="s">
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="16">
+    <row r="36" spans="1:28" ht="16">
       <c r="A36" s="2" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>795</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>246</v>
@@ -6940,59 +6981,60 @@
       <c r="I36" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="2"/>
+      <c r="K36" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="L36" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L36" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="N36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="P36" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="Q36" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="R36" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="R36" s="2">
+      <c r="S36" s="6">
         <v>1</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="T36" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="U36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U36" s="2" t="s">
+      <c r="V36" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V36" s="2" t="s">
+      <c r="W36" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2" t="s">
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:28">
       <c r="A37" s="2" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>785</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>794</v>
@@ -7006,59 +7048,60 @@
       <c r="I37" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J37" s="2"/>
+      <c r="K37" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="L37" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="N37" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="P37" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="Q37" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="R37" s="2">
+      <c r="S37" s="6">
         <v>2</v>
       </c>
-      <c r="S37" s="2" t="s">
+      <c r="T37" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="T37" s="2" t="s">
+      <c r="U37" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U37" s="2" t="s">
+      <c r="V37" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V37" s="2" t="s">
+      <c r="W37" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="2" t="s">
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="2" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="16">
+    <row r="38" spans="1:28" ht="16">
       <c r="A38" s="2" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>774</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>784</v>
@@ -7072,59 +7115,60 @@
       <c r="I38" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="2"/>
+      <c r="K38" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="L38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N38" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="R38" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="6">
         <v>2</v>
       </c>
-      <c r="S38" s="2" t="s">
+      <c r="T38" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="T38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U38" s="2" t="s">
+      <c r="V38" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="V38" s="2" t="s">
+      <c r="W38" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="Z38" s="2"/>
-      <c r="AA38" s="2" t="s">
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="16">
+    <row r="39" spans="1:28" ht="16">
       <c r="A39" s="2" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>763</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>773</v>
@@ -7138,59 +7182,60 @@
       <c r="I39" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="2"/>
+      <c r="K39" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="L39" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="N39" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L39" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="N39" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="P39" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="P39" s="2" t="s">
+      <c r="Q39" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="R39" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="R39" s="2">
+      <c r="S39" s="6">
         <v>1</v>
       </c>
-      <c r="S39" s="2" t="s">
+      <c r="T39" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="T39" s="2" t="s">
+      <c r="U39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U39" s="2" t="s">
+      <c r="V39" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V39" s="2" t="s">
+      <c r="W39" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="Z39" s="2"/>
-      <c r="AA39" s="2" t="s">
+      <c r="AA39" s="2"/>
+      <c r="AB39" s="2" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="16">
+    <row r="40" spans="1:28" ht="16">
       <c r="A40" s="2" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>757</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>762</v>
@@ -7204,59 +7249,60 @@
       <c r="I40" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="2"/>
+      <c r="K40" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="O40" s="2" t="s">
+      <c r="P40" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="P40" s="2" t="s">
+      <c r="Q40" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="Q40" s="2" t="s">
+      <c r="R40" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="R40" s="2">
+      <c r="S40" s="6">
         <v>2</v>
       </c>
-      <c r="S40" s="2" t="s">
+      <c r="T40" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="T40" s="2" t="s">
+      <c r="U40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U40" s="2" t="s">
+      <c r="V40" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V40" s="2" t="s">
+      <c r="W40" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="Z40" s="2"/>
-      <c r="AA40" s="2" t="s">
+      <c r="AA40" s="2"/>
+      <c r="AB40" s="2" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="16">
+    <row r="41" spans="1:28" ht="16">
       <c r="A41" s="2" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>748</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>756</v>
@@ -7270,59 +7316,60 @@
       <c r="I41" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="2"/>
+      <c r="K41" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="L41" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="N41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="N41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="O41" s="2" t="s">
+      <c r="P41" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="P41" s="2" t="s">
+      <c r="Q41" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="Q41" s="2" t="s">
+      <c r="R41" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="R41" s="2">
+      <c r="S41" s="6">
         <v>1</v>
       </c>
-      <c r="S41" s="2" t="s">
+      <c r="T41" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="T41" s="2" t="s">
+      <c r="U41" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U41" s="2" t="s">
+      <c r="V41" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V41" s="2" t="s">
+      <c r="W41" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="Z41" s="2"/>
-      <c r="AA41" s="2" t="s">
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="2" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="16">
+    <row r="42" spans="1:28" ht="16">
       <c r="A42" s="2" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>741</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>747</v>
@@ -7336,59 +7383,60 @@
       <c r="I42" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="2"/>
+      <c r="K42" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="L42" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="N42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="N42" s="2" t="s">
+      <c r="O42" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="O42" s="2" t="s">
+      <c r="P42" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="P42" s="2" t="s">
+      <c r="Q42" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="Q42" s="2" t="s">
+      <c r="R42" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="R42" s="2">
+      <c r="S42" s="6">
         <v>4</v>
       </c>
-      <c r="S42" s="2" t="s">
+      <c r="T42" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="T42" s="2" t="s">
+      <c r="U42" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U42" s="2" t="s">
+      <c r="V42" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V42" s="2" t="s">
+      <c r="W42" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="Z42" s="2"/>
-      <c r="AA42" s="2" t="s">
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="16">
+    <row r="43" spans="1:28" ht="16">
       <c r="A43" s="2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>730</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>740</v>
@@ -7402,59 +7450,60 @@
       <c r="I43" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="2"/>
+      <c r="K43" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="L43" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="N43" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="N43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="O43" s="2" t="s">
+      <c r="P43" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="P43" s="2" t="s">
+      <c r="Q43" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="R43" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="R43" s="2">
+      <c r="S43" s="6">
         <v>2</v>
       </c>
-      <c r="S43" s="2" t="s">
+      <c r="T43" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="T43" s="2" t="s">
+      <c r="U43" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U43" s="2" t="s">
+      <c r="V43" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V43" s="2" t="s">
+      <c r="W43" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="Z43" s="2"/>
-      <c r="AA43" s="2" t="s">
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="16">
+    <row r="44" spans="1:28" ht="16">
       <c r="A44" s="2" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>720</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>729</v>
@@ -7468,59 +7517,60 @@
       <c r="I44" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="2"/>
+      <c r="K44" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="L44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="O44" s="2" t="s">
+      <c r="P44" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="P44" s="2" t="s">
+      <c r="Q44" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="Q44" s="2" t="s">
+      <c r="R44" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="R44" s="2">
+      <c r="S44" s="6">
         <v>1</v>
       </c>
-      <c r="S44" s="2" t="s">
+      <c r="T44" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="T44" s="2" t="s">
+      <c r="U44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U44" s="2" t="s">
+      <c r="V44" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V44" s="2" t="s">
+      <c r="W44" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="Z44" s="2"/>
-      <c r="AA44" s="2" t="s">
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="2" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="16">
+    <row r="45" spans="1:28" ht="16">
       <c r="A45" s="2" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>708</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>719</v>
@@ -7534,59 +7584,60 @@
       <c r="I45" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="2"/>
+      <c r="K45" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="L45" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N45" s="2" t="s">
+      <c r="O45" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="O45" s="2" t="s">
+      <c r="P45" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="P45" s="2" t="s">
+      <c r="Q45" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="Q45" s="2" t="s">
+      <c r="R45" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="R45" s="2">
+      <c r="S45" s="6">
         <v>3</v>
       </c>
-      <c r="S45" s="2" t="s">
+      <c r="T45" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="T45" s="2" t="s">
+      <c r="U45" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U45" s="2" t="s">
+      <c r="V45" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="V45" s="2" t="s">
+      <c r="W45" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="Z45" s="2"/>
-      <c r="AA45" s="2" t="s">
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="2" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="16">
+    <row r="46" spans="1:28" ht="16">
       <c r="A46" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>707</v>
@@ -7600,59 +7651,60 @@
       <c r="I46" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="2"/>
+      <c r="K46" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="L46" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="N46" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="Q46" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="R46" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R46" s="2">
+      <c r="S46" s="6">
         <v>3</v>
       </c>
-      <c r="S46" s="2" t="s">
+      <c r="T46" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="T46" s="2" t="s">
+      <c r="U46" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="U46" s="2" t="s">
+      <c r="V46" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="V46" s="2" t="s">
+      <c r="W46" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2" t="s">
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="16">
+    <row r="47" spans="1:28" ht="16">
       <c r="A47" s="2" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>685</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>695</v>
@@ -7666,59 +7718,60 @@
       <c r="I47" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="2"/>
+      <c r="K47" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="L47" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="N47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="N47" s="2" t="s">
+      <c r="O47" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="O47" s="2" t="s">
+      <c r="P47" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="P47" s="2" t="s">
+      <c r="Q47" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="Q47" s="2" t="s">
+      <c r="R47" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R47" s="2">
+      <c r="S47" s="6">
         <v>2</v>
       </c>
-      <c r="S47" s="2" t="s">
+      <c r="T47" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="T47" s="2" t="s">
+      <c r="U47" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U47" s="2" t="s">
+      <c r="V47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V47" s="2" t="s">
+      <c r="W47" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="2" t="s">
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:28">
       <c r="A48" s="2" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>676</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>684</v>
@@ -7732,59 +7785,60 @@
       <c r="I48" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J48" s="2"/>
+      <c r="K48" s="6">
         <v>8000</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="L48" s="6">
+        <v>70000</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L48" s="4">
-        <v>70000</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="N48" s="2" t="s">
+      <c r="O48" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="P48" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P48" s="2" t="s">
+      <c r="Q48" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="Q48" s="2" t="s">
+      <c r="R48" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="R48" s="2">
+      <c r="S48" s="6">
         <v>3</v>
       </c>
-      <c r="S48" s="2" t="s">
+      <c r="T48" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="T48" s="2" t="s">
+      <c r="U48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="V48" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="V48" s="2" t="s">
+      <c r="W48" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="Z48" s="2"/>
-      <c r="AA48" s="2" t="s">
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:28">
       <c r="A49" s="2" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>666</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>675</v>
@@ -7798,59 +7852,60 @@
       <c r="I49" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="J49" s="4">
+      <c r="J49" s="2"/>
+      <c r="K49" s="6">
         <v>25000</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="L49" s="6">
+        <v>180000</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="N49" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L49" s="4">
-        <v>180000</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="N49" s="2" t="s">
+      <c r="O49" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="O49" s="2" t="s">
+      <c r="P49" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="P49" s="2" t="s">
+      <c r="Q49" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="Q49" s="2" t="s">
+      <c r="R49" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="R49" s="2">
+      <c r="S49" s="6">
         <v>3</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="T49" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="T49" s="2" t="s">
+      <c r="U49" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U49" s="2" t="s">
+      <c r="V49" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V49" s="2" t="s">
+      <c r="W49" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="Z49" s="2"/>
-      <c r="AA49" s="2" t="s">
+      <c r="AA49" s="2"/>
+      <c r="AB49" s="2" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="16">
+    <row r="50" spans="1:28" ht="16">
       <c r="A50" s="2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>654</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>665</v>
@@ -7864,59 +7919,60 @@
       <c r="I50" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="2"/>
+      <c r="K50" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="L50" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="N50" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L50" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="N50" s="2" t="s">
+      <c r="O50" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="O50" s="2" t="s">
+      <c r="P50" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P50" s="2" t="s">
+      <c r="Q50" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="Q50" s="2" t="s">
+      <c r="R50" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="R50" s="2">
+      <c r="S50" s="6">
         <v>2</v>
       </c>
-      <c r="S50" s="2" t="s">
+      <c r="T50" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="T50" s="2" t="s">
+      <c r="U50" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U50" s="2" t="s">
+      <c r="V50" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="V50" s="2" t="s">
+      <c r="W50" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="Z50" s="2"/>
-      <c r="AA50" s="2" t="s">
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="16">
+    <row r="51" spans="1:28" ht="16">
       <c r="A51" s="2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>643</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>653</v>
@@ -7930,59 +7986,60 @@
       <c r="I51" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="2"/>
+      <c r="K51" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="L51" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="N51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L51" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="N51" s="2" t="s">
+      <c r="O51" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="O51" s="2" t="s">
+      <c r="P51" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P51" s="2" t="s">
+      <c r="Q51" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="Q51" s="2" t="s">
+      <c r="R51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R51" s="2">
+      <c r="S51" s="6">
         <v>5</v>
       </c>
-      <c r="S51" s="2" t="s">
+      <c r="T51" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="T51" s="2" t="s">
+      <c r="U51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U51" s="2" t="s">
+      <c r="V51" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="V51" s="2" t="s">
+      <c r="W51" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="Z51" s="2"/>
-      <c r="AA51" s="2" t="s">
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="16">
+    <row r="52" spans="1:28" ht="16">
       <c r="A52" s="2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>634</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>642</v>
@@ -7996,59 +8053,60 @@
       <c r="I52" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="2"/>
+      <c r="K52" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="L52" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N52" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N52" s="2" t="s">
+      <c r="O52" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="O52" s="2" t="s">
+      <c r="P52" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="P52" s="2" t="s">
+      <c r="Q52" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="Q52" s="2" t="s">
+      <c r="R52" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R52" s="2">
+      <c r="S52" s="6">
         <v>2</v>
       </c>
-      <c r="S52" s="2" t="s">
+      <c r="T52" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="T52" s="2" t="s">
+      <c r="U52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U52" s="2" t="s">
+      <c r="V52" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="V52" s="2" t="s">
+      <c r="W52" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="Z52" s="2"/>
-      <c r="AA52" s="2" t="s">
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="16">
+    <row r="53" spans="1:28" ht="16">
       <c r="A53" s="2" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>624</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>633</v>
@@ -8062,59 +8120,60 @@
       <c r="I53" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="J53" s="4">
+      <c r="J53" s="2"/>
+      <c r="K53" s="6">
         <v>22000</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="L53" s="6">
+        <v>250000</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N53" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L53" s="4">
-        <v>250000</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N53" s="2" t="s">
+      <c r="O53" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="O53" s="2" t="s">
+      <c r="P53" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P53" s="2" t="s">
+      <c r="Q53" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="Q53" s="2" t="s">
+      <c r="R53" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="R53" s="2">
+      <c r="S53" s="6">
         <v>3</v>
       </c>
-      <c r="S53" s="2" t="s">
+      <c r="T53" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="T53" s="2" t="s">
+      <c r="U53" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U53" s="2" t="s">
+      <c r="V53" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="V53" s="2" t="s">
+      <c r="W53" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="Z53" s="2"/>
-      <c r="AA53" s="2" t="s">
+      <c r="AA53" s="2"/>
+      <c r="AB53" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="16">
+    <row r="54" spans="1:28" ht="16">
       <c r="A54" s="2" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>613</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>623</v>
@@ -8128,59 +8187,60 @@
       <c r="I54" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="2"/>
+      <c r="K54" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="L54" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N54" s="2" t="s">
+      <c r="O54" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="O54" s="2" t="s">
+      <c r="P54" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="Q54" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="Q54" s="2" t="s">
+      <c r="R54" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R54" s="2">
+      <c r="S54" s="6">
         <v>5</v>
       </c>
-      <c r="S54" s="2" t="s">
+      <c r="T54" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="T54" s="2" t="s">
+      <c r="U54" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U54" s="2" t="s">
+      <c r="V54" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="V54" s="2" t="s">
+      <c r="W54" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="Z54" s="2"/>
-      <c r="AA54" s="2" t="s">
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:28">
       <c r="A55" s="2" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>599</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>612</v>
@@ -8194,59 +8254,60 @@
       <c r="I55" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="J55" s="2"/>
+      <c r="K55" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="L55" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="N55" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L55" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="N55" s="2" t="s">
+      <c r="O55" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="O55" s="2" t="s">
+      <c r="P55" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="P55" s="2" t="s">
+      <c r="Q55" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="Q55" s="2" t="s">
+      <c r="R55" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="R55" s="2">
+      <c r="S55" s="6">
         <v>2</v>
       </c>
-      <c r="S55" s="2" t="s">
+      <c r="T55" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="T55" s="2" t="s">
+      <c r="U55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U55" s="2" t="s">
+      <c r="V55" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="V55" s="2" t="s">
+      <c r="W55" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="Z55" s="2"/>
-      <c r="AA55" s="2" t="s">
+      <c r="AA55" s="2"/>
+      <c r="AB55" s="2" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:28">
       <c r="A56" s="2" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>588</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>598</v>
@@ -8260,59 +8321,60 @@
       <c r="I56" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="J56" s="4">
+      <c r="J56" s="2"/>
+      <c r="K56" s="6">
         <v>58000</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="L56" s="6">
+        <v>420000</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N56" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L56" s="4">
-        <v>420000</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="N56" s="2" t="s">
+      <c r="O56" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="O56" s="2" t="s">
+      <c r="P56" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="P56" s="2" t="s">
+      <c r="Q56" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="Q56" s="2" t="s">
+      <c r="R56" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="R56" s="2">
+      <c r="S56" s="6">
         <v>2</v>
       </c>
-      <c r="S56" s="2" t="s">
+      <c r="T56" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="T56" s="2" t="s">
+      <c r="U56" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U56" s="2" t="s">
+      <c r="V56" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="V56" s="2" t="s">
+      <c r="W56" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="Z56" s="2"/>
-      <c r="AA56" s="2" t="s">
+      <c r="AA56" s="2"/>
+      <c r="AB56" s="2" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="16">
+    <row r="57" spans="1:28" ht="16">
       <c r="A57" s="2" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>576</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>587</v>
@@ -8326,59 +8388,60 @@
       <c r="I57" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="2"/>
+      <c r="K57" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="L57" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="N57" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="N57" s="2" t="s">
+      <c r="O57" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="O57" s="2" t="s">
+      <c r="P57" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P57" s="2" t="s">
+      <c r="Q57" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="Q57" s="2" t="s">
+      <c r="R57" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R57" s="2">
+      <c r="S57" s="6">
         <v>4</v>
       </c>
-      <c r="S57" s="2" t="s">
+      <c r="T57" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="T57" s="2" t="s">
+      <c r="U57" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U57" s="2" t="s">
+      <c r="V57" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="V57" s="2" t="s">
+      <c r="W57" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="Z57" s="2"/>
-      <c r="AA57" s="2" t="s">
+      <c r="AA57" s="2"/>
+      <c r="AB57" s="2" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:28">
       <c r="A58" s="2" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>567</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>575</v>
@@ -8392,59 +8455,60 @@
       <c r="I58" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="J58" s="4">
+      <c r="J58" s="2"/>
+      <c r="K58" s="6">
         <v>9000</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="L58" s="6">
+        <v>30000</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="N58" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L58" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="N58" s="2" t="s">
+      <c r="O58" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="O58" s="2" t="s">
+      <c r="P58" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="P58" s="2" t="s">
+      <c r="Q58" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="Q58" s="2" t="s">
+      <c r="R58" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="R58" s="2">
+      <c r="S58" s="6">
         <v>1</v>
       </c>
-      <c r="S58" s="2" t="s">
+      <c r="T58" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="T58" s="2" t="s">
+      <c r="U58" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="U58" s="2" t="s">
+      <c r="V58" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="V58" s="2" t="s">
+      <c r="W58" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="Z58" s="2"/>
-      <c r="AA58" s="2" t="s">
+      <c r="AA58" s="2"/>
+      <c r="AB58" s="2" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="16">
+    <row r="59" spans="1:28" ht="16">
       <c r="A59" s="2" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>553</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>566</v>
@@ -8458,59 +8522,60 @@
       <c r="I59" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="2"/>
+      <c r="K59" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="L59" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="N59" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L59" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="N59" s="2" t="s">
+      <c r="O59" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="O59" s="2" t="s">
+      <c r="P59" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="P59" s="2" t="s">
+      <c r="Q59" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="Q59" s="2" t="s">
+      <c r="R59" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="R59" s="2">
+      <c r="S59" s="6">
         <v>5</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="T59" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="T59" s="2" t="s">
+      <c r="U59" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U59" s="2" t="s">
+      <c r="V59" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="V59" s="2" t="s">
+      <c r="W59" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="Z59" s="2"/>
-      <c r="AA59" s="2" t="s">
+      <c r="AA59" s="2"/>
+      <c r="AB59" s="2" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:28">
       <c r="A60" s="2" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>541</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>552</v>
@@ -8524,59 +8589,60 @@
       <c r="I60" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="J60" s="4">
+      <c r="J60" s="2"/>
+      <c r="K60" s="6">
         <v>20000</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="L60" s="6">
+        <v>140000</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N60" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L60" s="4">
-        <v>140000</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="N60" s="2" t="s">
+      <c r="O60" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="O60" s="2" t="s">
+      <c r="P60" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P60" s="2" t="s">
+      <c r="Q60" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="Q60" s="2" t="s">
+      <c r="R60" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="R60" s="2">
+      <c r="S60" s="6">
         <v>2</v>
       </c>
-      <c r="S60" s="2" t="s">
+      <c r="T60" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="T60" s="2" t="s">
+      <c r="U60" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U60" s="2" t="s">
+      <c r="V60" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="V60" s="2" t="s">
+      <c r="W60" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="Z60" s="2"/>
-      <c r="AA60" s="2" t="s">
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="2" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="16">
+    <row r="61" spans="1:28" ht="16">
       <c r="A61" s="2" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>530</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>436</v>
@@ -8590,59 +8656,60 @@
       <c r="I61" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="2"/>
+      <c r="K61" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="L61" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N61" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N61" s="2" t="s">
+      <c r="O61" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="O61" s="2" t="s">
+      <c r="P61" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P61" s="2" t="s">
+      <c r="Q61" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="Q61" s="2" t="s">
+      <c r="R61" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="R61" s="2">
+      <c r="S61" s="6">
         <v>1</v>
       </c>
-      <c r="S61" s="2" t="s">
+      <c r="T61" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="T61" s="2" t="s">
+      <c r="U61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U61" s="2" t="s">
+      <c r="V61" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="V61" s="2" t="s">
+      <c r="W61" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="Z61" s="2"/>
-      <c r="AA61" s="2" t="s">
+      <c r="AA61" s="2"/>
+      <c r="AB61" s="2" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="16">
+    <row r="62" spans="1:28" ht="16">
       <c r="A62" s="2" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>521</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>529</v>
@@ -8656,59 +8723,60 @@
       <c r="I62" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="2"/>
+      <c r="K62" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="L62" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="N62" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L62" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="N62" s="2" t="s">
+      <c r="O62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="P62" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="Q62" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="Q62" s="2" t="s">
+      <c r="R62" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R62" s="2">
+      <c r="S62" s="6">
         <v>5</v>
       </c>
-      <c r="S62" s="2" t="s">
+      <c r="T62" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="T62" s="2" t="s">
+      <c r="U62" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U62" s="2" t="s">
+      <c r="V62" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="V62" s="2" t="s">
+      <c r="W62" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="Z62" s="2"/>
-      <c r="AA62" s="2" t="s">
+      <c r="AA62" s="2"/>
+      <c r="AB62" s="2" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="63" spans="1:27">
+    <row r="63" spans="1:28">
       <c r="A63" s="2" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>510</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>520</v>
@@ -8722,59 +8790,60 @@
       <c r="I63" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="J63" s="4">
+      <c r="J63" s="2"/>
+      <c r="K63" s="6">
         <v>25000</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="L63" s="6">
+        <v>220000</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="N63" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L63" s="4">
-        <v>220000</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="N63" s="2" t="s">
+      <c r="O63" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="O63" s="2" t="s">
+      <c r="P63" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P63" s="2" t="s">
+      <c r="Q63" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="Q63" s="2" t="s">
+      <c r="R63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R63" s="2">
+      <c r="S63" s="6">
         <v>3</v>
       </c>
-      <c r="S63" s="2" t="s">
+      <c r="T63" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="T63" s="2" t="s">
+      <c r="U63" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U63" s="2" t="s">
+      <c r="V63" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="V63" s="2" t="s">
+      <c r="W63" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="Z63" s="2"/>
-      <c r="AA63" s="2" t="s">
+      <c r="AA63" s="2"/>
+      <c r="AB63" s="2" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="16">
+    <row r="64" spans="1:28" ht="16">
       <c r="A64" s="2" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>500</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>509</v>
@@ -8788,59 +8857,60 @@
       <c r="I64" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="2"/>
+      <c r="K64" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="L64" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="N64" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L64" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="N64" s="2" t="s">
+      <c r="O64" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="O64" s="2" t="s">
+      <c r="P64" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P64" s="2" t="s">
+      <c r="Q64" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="Q64" s="2" t="s">
+      <c r="R64" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="R64" s="2">
+      <c r="S64" s="6">
         <v>2</v>
       </c>
-      <c r="S64" s="2" t="s">
+      <c r="T64" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="T64" s="2" t="s">
+      <c r="U64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U64" s="2" t="s">
+      <c r="V64" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="V64" s="2" t="s">
+      <c r="W64" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="Z64" s="2"/>
-      <c r="AA64" s="2" t="s">
+      <c r="AA64" s="2"/>
+      <c r="AB64" s="2" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="16">
+    <row r="65" spans="1:28" ht="16">
       <c r="A65" s="2" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>490</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>499</v>
@@ -8854,59 +8924,60 @@
       <c r="I65" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="2"/>
+      <c r="K65" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="L65" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N65" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N65" s="2" t="s">
+      <c r="O65" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="O65" s="2" t="s">
+      <c r="P65" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P65" s="2" t="s">
+      <c r="Q65" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="Q65" s="2" t="s">
+      <c r="R65" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="R65" s="2">
+      <c r="S65" s="6">
         <v>3</v>
       </c>
-      <c r="S65" s="2" t="s">
+      <c r="T65" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="T65" s="2" t="s">
+      <c r="U65" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U65" s="2" t="s">
+      <c r="V65" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="V65" s="2" t="s">
+      <c r="W65" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="Z65" s="2"/>
-      <c r="AA65" s="2" t="s">
+      <c r="AA65" s="2"/>
+      <c r="AB65" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="16">
+    <row r="66" spans="1:28" ht="16">
       <c r="A66" s="2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>479</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>489</v>
@@ -8920,59 +8991,60 @@
       <c r="I66" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="2"/>
+      <c r="K66" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="L66" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N66" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N66" s="2" t="s">
+      <c r="O66" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="O66" s="2" t="s">
+      <c r="P66" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="P66" s="2" t="s">
+      <c r="Q66" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="Q66" s="2" t="s">
+      <c r="R66" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R66" s="2">
+      <c r="S66" s="6">
         <v>4</v>
       </c>
-      <c r="S66" s="2" t="s">
+      <c r="T66" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="T66" s="2" t="s">
+      <c r="U66" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U66" s="2" t="s">
+      <c r="V66" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="V66" s="2" t="s">
+      <c r="W66" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="Z66" s="2"/>
-      <c r="AA66" s="2" t="s">
+      <c r="AA66" s="2"/>
+      <c r="AB66" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="1:27">
+    <row r="67" spans="1:28">
       <c r="A67" s="2" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>471</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>478</v>
@@ -8986,59 +9058,60 @@
       <c r="I67" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="J67" s="4">
+      <c r="J67" s="2"/>
+      <c r="K67" s="6">
         <v>40000</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="L67" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="N67" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L67" s="4">
-        <v>400000</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="N67" s="2" t="s">
+      <c r="O67" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O67" s="2" t="s">
+      <c r="P67" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P67" s="2" t="s">
+      <c r="Q67" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="Q67" s="2" t="s">
+      <c r="R67" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="R67" s="2">
+      <c r="S67" s="6">
         <v>2</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="T67" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="T67" s="2" t="s">
+      <c r="U67" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U67" s="2" t="s">
+      <c r="V67" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="V67" s="2" t="s">
+      <c r="W67" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="Z67" s="2"/>
-      <c r="AA67" s="2" t="s">
+      <c r="AA67" s="2"/>
+      <c r="AB67" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="16">
+    <row r="68" spans="1:28" ht="16">
       <c r="A68" s="2" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>459</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>470</v>
@@ -9052,59 +9125,60 @@
       <c r="I68" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="2"/>
+      <c r="K68" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="L68" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N68" s="2" t="s">
+      <c r="O68" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="O68" s="2" t="s">
+      <c r="P68" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="P68" s="2" t="s">
+      <c r="Q68" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="Q68" s="2" t="s">
+      <c r="R68" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="R68" s="2">
+      <c r="S68" s="6">
         <v>1</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="T68" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="T68" s="2" t="s">
+      <c r="U68" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U68" s="2" t="s">
+      <c r="V68" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="V68" s="2" t="s">
+      <c r="W68" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="Z68" s="2"/>
-      <c r="AA68" s="2" t="s">
+      <c r="AA68" s="2"/>
+      <c r="AB68" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="16">
+    <row r="69" spans="1:28" ht="16">
       <c r="A69" s="2" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>448</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>458</v>
@@ -9118,59 +9192,60 @@
       <c r="I69" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="2"/>
+      <c r="K69" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="L69" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N69" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L69" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N69" s="2" t="s">
+      <c r="O69" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="O69" s="2" t="s">
+      <c r="P69" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="P69" s="2" t="s">
+      <c r="Q69" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="Q69" s="2" t="s">
+      <c r="R69" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="R69" s="2">
+      <c r="S69" s="6">
         <v>3</v>
       </c>
-      <c r="S69" s="2" t="s">
+      <c r="T69" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="T69" s="2" t="s">
+      <c r="U69" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U69" s="2" t="s">
+      <c r="V69" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="V69" s="2" t="s">
+      <c r="W69" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="Z69" s="2"/>
-      <c r="AA69" s="2" t="s">
+      <c r="AA69" s="2"/>
+      <c r="AB69" s="2" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="16">
+    <row r="70" spans="1:28" ht="16">
       <c r="A70" s="2" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>437</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>447</v>
@@ -9184,59 +9259,60 @@
       <c r="I70" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="2"/>
+      <c r="K70" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="L70" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="N70" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="N70" s="2" t="s">
+      <c r="O70" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="O70" s="2" t="s">
+      <c r="P70" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P70" s="2" t="s">
+      <c r="Q70" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="Q70" s="2" t="s">
+      <c r="R70" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="R70" s="2">
+      <c r="S70" s="6">
         <v>3</v>
       </c>
-      <c r="S70" s="2" t="s">
+      <c r="T70" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="T70" s="2" t="s">
+      <c r="U70" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U70" s="2" t="s">
+      <c r="V70" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="V70" s="2" t="s">
+      <c r="W70" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="Z70" s="2"/>
-      <c r="AA70" s="2" t="s">
+      <c r="AA70" s="2"/>
+      <c r="AB70" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="71" spans="1:27">
+    <row r="71" spans="1:28">
       <c r="A71" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>424</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>436</v>
@@ -9250,59 +9326,60 @@
       <c r="I71" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="J71" s="4">
+      <c r="J71" s="2"/>
+      <c r="K71" s="6">
         <v>12000</v>
       </c>
-      <c r="K71" s="2" t="s">
+      <c r="L71" s="6">
+        <v>90000</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="N71" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L71" s="4">
-        <v>90000</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="N71" s="2" t="s">
+      <c r="O71" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="O71" s="2" t="s">
+      <c r="P71" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="P71" s="2" t="s">
+      <c r="Q71" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="Q71" s="2" t="s">
+      <c r="R71" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="R71" s="2">
+      <c r="S71" s="6">
         <v>1</v>
       </c>
-      <c r="S71" s="2" t="s">
+      <c r="T71" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="T71" s="2" t="s">
+      <c r="U71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U71" s="2" t="s">
+      <c r="V71" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="V71" s="2" t="s">
+      <c r="W71" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="Z71" s="2"/>
-      <c r="AA71" s="2" t="s">
+      <c r="AA71" s="2"/>
+      <c r="AB71" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="16">
+    <row r="72" spans="1:28" ht="16">
       <c r="A72" s="2" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>410</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>423</v>
@@ -9316,59 +9393,60 @@
       <c r="I72" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="2"/>
+      <c r="K72" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="L72" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N72" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L72" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N72" s="2" t="s">
+      <c r="O72" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="O72" s="2" t="s">
+      <c r="P72" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="P72" s="2" t="s">
+      <c r="Q72" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="Q72" s="2" t="s">
+      <c r="R72" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="R72" s="2">
+      <c r="S72" s="6">
         <v>2</v>
       </c>
-      <c r="S72" s="2" t="s">
+      <c r="T72" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="T72" s="2" t="s">
+      <c r="U72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U72" s="2" t="s">
+      <c r="V72" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="V72" s="2" t="s">
+      <c r="W72" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="Z72" s="2"/>
-      <c r="AA72" s="2" t="s">
+      <c r="AA72" s="2"/>
+      <c r="AB72" s="2" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="16">
+    <row r="73" spans="1:28" ht="16">
       <c r="A73" s="2" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>409</v>
@@ -9382,59 +9460,60 @@
       <c r="I73" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="2"/>
+      <c r="K73" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="L73" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N73" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L73" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N73" s="2" t="s">
+      <c r="O73" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="O73" s="2" t="s">
+      <c r="P73" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P73" s="2" t="s">
+      <c r="Q73" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="Q73" s="2" t="s">
+      <c r="R73" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="R73" s="2">
+      <c r="S73" s="6">
         <v>2</v>
       </c>
-      <c r="S73" s="2" t="s">
+      <c r="T73" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="T73" s="2" t="s">
+      <c r="U73" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U73" s="2" t="s">
+      <c r="V73" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="V73" s="2" t="s">
+      <c r="W73" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="Z73" s="2"/>
-      <c r="AA73" s="2" t="s">
+      <c r="AA73" s="2"/>
+      <c r="AB73" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="16">
+    <row r="74" spans="1:28" ht="16">
       <c r="A74" s="2" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>386</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>396</v>
@@ -9448,59 +9527,60 @@
       <c r="I74" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="J74" s="2"/>
+      <c r="K74" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="L74" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="N74" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L74" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N74" s="2" t="s">
+      <c r="O74" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="O74" s="2" t="s">
+      <c r="P74" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="P74" s="2" t="s">
+      <c r="Q74" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="Q74" s="2" t="s">
+      <c r="R74" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="R74" s="2">
+      <c r="S74" s="6">
         <v>2</v>
       </c>
-      <c r="S74" s="2" t="s">
+      <c r="T74" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="T74" s="2" t="s">
+      <c r="U74" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U74" s="2" t="s">
+      <c r="V74" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="V74" s="2" t="s">
+      <c r="W74" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="Z74" s="2"/>
-      <c r="AA74" s="2" t="s">
+      <c r="AA74" s="2"/>
+      <c r="AB74" s="2" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="75" spans="1:27">
+    <row r="75" spans="1:28">
       <c r="A75" s="2" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>377</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>385</v>
@@ -9514,59 +9594,60 @@
       <c r="I75" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="2"/>
+      <c r="K75" s="6">
         <v>45000</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="L75" s="6">
+        <v>400000</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N75" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L75" s="4">
-        <v>400000</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="N75" s="2" t="s">
+      <c r="O75" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="O75" s="2" t="s">
+      <c r="P75" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P75" s="2" t="s">
+      <c r="Q75" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="Q75" s="2" t="s">
+      <c r="R75" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="R75" s="2">
+      <c r="S75" s="6">
         <v>2</v>
       </c>
-      <c r="S75" s="2" t="s">
+      <c r="T75" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="T75" s="2" t="s">
+      <c r="U75" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U75" s="2" t="s">
+      <c r="V75" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="V75" s="2" t="s">
+      <c r="W75" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="Z75" s="2"/>
-      <c r="AA75" s="2" t="s">
+      <c r="AA75" s="2"/>
+      <c r="AB75" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="16">
+    <row r="76" spans="1:28" ht="16">
       <c r="A76" s="2" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>367</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>376</v>
@@ -9580,59 +9661,60 @@
       <c r="I76" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="2"/>
+      <c r="K76" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="L76" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N76" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N76" s="2" t="s">
+      <c r="O76" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="O76" s="2" t="s">
+      <c r="P76" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P76" s="2" t="s">
+      <c r="Q76" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="Q76" s="2" t="s">
+      <c r="R76" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="R76" s="2">
+      <c r="S76" s="6">
         <v>3</v>
       </c>
-      <c r="S76" s="2" t="s">
+      <c r="T76" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="T76" s="2" t="s">
+      <c r="U76" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U76" s="2" t="s">
+      <c r="V76" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V76" s="2" t="s">
+      <c r="W76" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="Z76" s="2"/>
-      <c r="AA76" s="2" t="s">
+      <c r="AA76" s="2"/>
+      <c r="AB76" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="16">
+    <row r="77" spans="1:28" ht="16">
       <c r="A77" s="2" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>366</v>
@@ -9646,59 +9728,60 @@
       <c r="I77" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="2"/>
+      <c r="K77" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="L77" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="M77" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N77" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L77" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N77" s="2" t="s">
+      <c r="O77" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="O77" s="2" t="s">
+      <c r="P77" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P77" s="2" t="s">
+      <c r="Q77" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="Q77" s="2" t="s">
+      <c r="R77" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="R77" s="2">
+      <c r="S77" s="6">
         <v>3</v>
       </c>
-      <c r="S77" s="2" t="s">
+      <c r="T77" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="T77" s="2" t="s">
+      <c r="U77" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U77" s="2" t="s">
+      <c r="V77" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="V77" s="2" t="s">
+      <c r="W77" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="Z77" s="2"/>
-      <c r="AA77" s="2" t="s">
+      <c r="AA77" s="2"/>
+      <c r="AB77" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="78" spans="1:27">
+    <row r="78" spans="1:28">
       <c r="A78" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>355</v>
@@ -9712,59 +9795,60 @@
       <c r="I78" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="J78" s="2"/>
+      <c r="K78" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="L78" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N78" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L78" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N78" s="2" t="s">
+      <c r="O78" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="O78" s="2" t="s">
+      <c r="P78" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P78" s="2" t="s">
+      <c r="Q78" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="Q78" s="2" t="s">
+      <c r="R78" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="R78" s="2">
+      <c r="S78" s="6">
         <v>5</v>
       </c>
-      <c r="S78" s="2" t="s">
+      <c r="T78" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="T78" s="2" t="s">
+      <c r="U78" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U78" s="2" t="s">
+      <c r="V78" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="V78" s="2" t="s">
+      <c r="W78" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="Z78" s="2"/>
-      <c r="AA78" s="2" t="s">
+      <c r="AA78" s="2"/>
+      <c r="AB78" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="79" spans="1:27">
+    <row r="79" spans="1:28">
       <c r="A79" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>344</v>
@@ -9778,59 +9862,60 @@
       <c r="I79" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="J79" s="4">
+      <c r="J79" s="2"/>
+      <c r="K79" s="6">
         <v>50000</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="L79" s="6">
+        <v>450000</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N79" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L79" s="4">
-        <v>450000</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="N79" s="2" t="s">
+      <c r="O79" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O79" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P79" s="2" t="s">
+      <c r="Q79" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="Q79" s="2" t="s">
+      <c r="R79" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="R79" s="2">
+      <c r="S79" s="6">
         <v>2</v>
       </c>
-      <c r="S79" s="2" t="s">
+      <c r="T79" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="T79" s="2" t="s">
+      <c r="U79" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U79" s="2" t="s">
+      <c r="V79" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="V79" s="2" t="s">
+      <c r="W79" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="Z79" s="2"/>
-      <c r="AA79" s="2" t="s">
+      <c r="AA79" s="2"/>
+      <c r="AB79" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:27">
+    <row r="80" spans="1:28">
       <c r="A80" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>319</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>333</v>
@@ -9844,59 +9929,60 @@
       <c r="I80" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="J80" s="4">
+      <c r="J80" s="2"/>
+      <c r="K80" s="6">
         <v>60000</v>
       </c>
-      <c r="K80" s="2" t="s">
+      <c r="L80" s="6">
+        <v>650000</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="N80" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L80" s="4">
-        <v>650000</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="N80" s="2" t="s">
+      <c r="O80" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="O80" s="2" t="s">
+      <c r="P80" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P80" s="2" t="s">
+      <c r="Q80" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="Q80" s="2" t="s">
+      <c r="R80" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="6">
         <v>15</v>
       </c>
-      <c r="S80" s="2" t="s">
+      <c r="T80" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="T80" s="2" t="s">
+      <c r="U80" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="U80" s="2" t="s">
+      <c r="V80" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="V80" s="2" t="s">
+      <c r="W80" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="Z80" s="2"/>
-      <c r="AA80" s="2" t="s">
+      <c r="AA80" s="2"/>
+      <c r="AB80" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="16">
+    <row r="81" spans="1:28" ht="16">
       <c r="A81" s="2" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>307</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>318</v>
@@ -9910,59 +9996,60 @@
       <c r="I81" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="2"/>
+      <c r="K81" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="L81" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="N81" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="N81" s="2" t="s">
+      <c r="O81" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O81" s="2" t="s">
+      <c r="P81" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P81" s="2" t="s">
+      <c r="Q81" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="Q81" s="2" t="s">
+      <c r="R81" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="R81" s="2">
+      <c r="S81" s="6">
         <v>4</v>
       </c>
-      <c r="S81" s="2" t="s">
+      <c r="T81" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="T81" s="2" t="s">
+      <c r="U81" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U81" s="2" t="s">
+      <c r="V81" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="V81" s="2" t="s">
+      <c r="W81" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="Z81" s="2"/>
-      <c r="AA81" s="2" t="s">
+      <c r="AA81" s="2"/>
+      <c r="AB81" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="16">
+    <row r="82" spans="1:28" ht="16">
       <c r="A82" s="2" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>292</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>306</v>
@@ -9976,59 +10063,60 @@
       <c r="I82" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="J82" s="2"/>
+      <c r="K82" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="K82" s="2" t="s">
+      <c r="L82" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="N82" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="N82" s="2" t="s">
+      <c r="O82" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="O82" s="2" t="s">
+      <c r="P82" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="P82" s="2" t="s">
+      <c r="Q82" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="Q82" s="2" t="s">
+      <c r="R82" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="R82" s="2">
+      <c r="S82" s="6">
         <v>3</v>
       </c>
-      <c r="S82" s="2" t="s">
+      <c r="T82" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="T82" s="2" t="s">
+      <c r="U82" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U82" s="2" t="s">
+      <c r="V82" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="V82" s="2" t="s">
+      <c r="W82" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="Z82" s="2"/>
-      <c r="AA82" s="2" t="s">
+      <c r="AA82" s="2"/>
+      <c r="AB82" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="16">
+    <row r="83" spans="1:28" ht="16">
       <c r="A83" s="2" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>279</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>291</v>
@@ -10042,59 +10130,60 @@
       <c r="I83" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="2"/>
+      <c r="K83" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="L83" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="N83" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L83" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="N83" s="2" t="s">
+      <c r="O83" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="O83" s="2" t="s">
+      <c r="P83" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P83" s="2" t="s">
+      <c r="Q83" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="Q83" s="2" t="s">
+      <c r="R83" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="R83" s="2">
+      <c r="S83" s="6">
         <v>1</v>
       </c>
-      <c r="S83" s="2" t="s">
+      <c r="T83" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="T83" s="2" t="s">
+      <c r="U83" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U83" s="2" t="s">
+      <c r="V83" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="V83" s="2" t="s">
+      <c r="W83" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="Z83" s="2"/>
-      <c r="AA83" s="2" t="s">
+      <c r="AA83" s="2"/>
+      <c r="AB83" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="16">
+    <row r="84" spans="1:28" ht="16">
       <c r="A84" s="2" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>278</v>
@@ -10108,59 +10197,60 @@
       <c r="I84" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="J84" s="2"/>
+      <c r="K84" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="K84" s="2" t="s">
+      <c r="L84" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="N84" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N84" s="2" t="s">
+      <c r="O84" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="O84" s="2" t="s">
+      <c r="P84" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="P84" s="2" t="s">
+      <c r="Q84" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="Q84" s="2" t="s">
+      <c r="R84" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="R84" s="2">
+      <c r="S84" s="6">
         <v>1</v>
       </c>
-      <c r="S84" s="2" t="s">
+      <c r="T84" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="T84" s="2" t="s">
+      <c r="U84" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="U84" s="2" t="s">
+      <c r="V84" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="V84" s="2" t="s">
+      <c r="W84" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="Z84" s="2"/>
-      <c r="AA84" s="2" t="s">
+      <c r="AA84" s="2"/>
+      <c r="AB84" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="16">
+    <row r="85" spans="1:28" ht="16">
       <c r="A85" s="2" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>262</v>
@@ -10174,59 +10264,60 @@
       <c r="I85" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="2"/>
+      <c r="K85" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="L85" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N85" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N85" s="2" t="s">
+      <c r="O85" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="O85" s="2" t="s">
+      <c r="P85" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="P85" s="2" t="s">
+      <c r="Q85" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="Q85" s="2" t="s">
+      <c r="R85" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="R85" s="2">
+      <c r="S85" s="6">
         <v>3</v>
       </c>
-      <c r="S85" s="2" t="s">
+      <c r="T85" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="T85" s="2" t="s">
+      <c r="U85" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U85" s="2" t="s">
+      <c r="V85" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="V85" s="2" t="s">
+      <c r="W85" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="Z85" s="2"/>
-      <c r="AA85" s="2" t="s">
+      <c r="AA85" s="2"/>
+      <c r="AB85" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="16">
+    <row r="86" spans="1:28" ht="16">
       <c r="A86" s="2" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>246</v>
@@ -10240,59 +10331,60 @@
       <c r="I86" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J86" s="4">
+      <c r="J86" s="2"/>
+      <c r="K86" s="6">
         <v>35000</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="L86" s="6">
+        <v>320000</v>
+      </c>
+      <c r="M86" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N86" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L86" s="4">
-        <v>320000</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="N86" s="2" t="s">
+      <c r="O86" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="O86" s="2" t="s">
+      <c r="P86" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P86" s="2" t="s">
+      <c r="Q86" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Q86" s="2" t="s">
+      <c r="R86" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="R86" s="2">
+      <c r="S86" s="6">
         <v>4</v>
       </c>
-      <c r="S86" s="2" t="s">
+      <c r="T86" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="T86" s="2" t="s">
+      <c r="U86" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U86" s="2" t="s">
+      <c r="V86" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="V86" s="2" t="s">
+      <c r="W86" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="Z86" s="2"/>
-      <c r="AA86" s="2" t="s">
+      <c r="AA86" s="2"/>
+      <c r="AB86" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:27">
+    <row r="87" spans="1:28">
       <c r="A87" s="2" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>235</v>
@@ -10306,59 +10398,60 @@
       <c r="I87" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J87" s="4">
+      <c r="J87" s="2"/>
+      <c r="K87" s="6">
         <v>20000</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="L87" s="6">
+        <v>180000</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="N87" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L87" s="4">
-        <v>180000</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="N87" s="2" t="s">
+      <c r="O87" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="O87" s="2" t="s">
+      <c r="P87" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P87" s="2" t="s">
+      <c r="Q87" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="Q87" s="2" t="s">
+      <c r="R87" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R87" s="2">
+      <c r="S87" s="6">
         <v>2</v>
       </c>
-      <c r="S87" s="2" t="s">
+      <c r="T87" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="T87" s="2" t="s">
+      <c r="U87" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U87" s="2" t="s">
+      <c r="V87" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="V87" s="2" t="s">
+      <c r="W87" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="Z87" s="2"/>
-      <c r="AA87" s="2" t="s">
+      <c r="AA87" s="2"/>
+      <c r="AB87" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="88" spans="1:27">
+    <row r="88" spans="1:28">
       <c r="A88" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>223</v>
@@ -10372,59 +10465,60 @@
       <c r="I88" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="J88" s="4">
+      <c r="J88" s="2"/>
+      <c r="K88" s="6">
         <v>15000</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="L88" s="6">
+        <v>90000</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="N88" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L88" s="4">
-        <v>90000</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="N88" s="2" t="s">
+      <c r="O88" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="O88" s="2" t="s">
+      <c r="P88" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="P88" s="2" t="s">
+      <c r="Q88" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="Q88" s="2" t="s">
+      <c r="R88" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R88" s="2">
+      <c r="S88" s="6">
         <v>6</v>
       </c>
-      <c r="S88" s="2" t="s">
+      <c r="T88" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="T88" s="2" t="s">
+      <c r="U88" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U88" s="2" t="s">
+      <c r="V88" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="V88" s="2" t="s">
+      <c r="W88" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="Z88" s="2"/>
-      <c r="AA88" s="2" t="s">
+      <c r="AA88" s="2"/>
+      <c r="AB88" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="16">
+    <row r="89" spans="1:28" ht="16">
       <c r="A89" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>212</v>
@@ -10438,59 +10532,60 @@
       <c r="I89" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="J89" s="2"/>
+      <c r="K89" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K89" s="2" t="s">
+      <c r="L89" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M89" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N89" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L89" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N89" s="2" t="s">
+      <c r="O89" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="O89" s="2" t="s">
+      <c r="P89" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P89" s="2" t="s">
+      <c r="Q89" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="Q89" s="2" t="s">
+      <c r="R89" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R89" s="2">
+      <c r="S89" s="6">
         <v>1</v>
       </c>
-      <c r="S89" s="2" t="s">
+      <c r="T89" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="T89" s="2" t="s">
+      <c r="U89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U89" s="2" t="s">
+      <c r="V89" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="V89" s="2" t="s">
+      <c r="W89" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="Z89" s="2"/>
-      <c r="AA89" s="2" t="s">
+      <c r="AA89" s="2"/>
+      <c r="AB89" s="2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="16">
+    <row r="90" spans="1:28" ht="16">
       <c r="A90" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>199</v>
@@ -10504,59 +10599,60 @@
       <c r="I90" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="J90" s="2"/>
+      <c r="K90" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="L90" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="N90" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L90" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="M90" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="N90" s="2" t="s">
+      <c r="O90" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="O90" s="2" t="s">
+      <c r="P90" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P90" s="2" t="s">
+      <c r="Q90" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="Q90" s="2" t="s">
+      <c r="R90" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="R90" s="2">
+      <c r="S90" s="6">
         <v>8</v>
       </c>
-      <c r="S90" s="2" t="s">
+      <c r="T90" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="T90" s="2" t="s">
+      <c r="U90" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U90" s="2" t="s">
+      <c r="V90" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="V90" s="2" t="s">
+      <c r="W90" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="Z90" s="2"/>
-      <c r="AA90" s="2" t="s">
+      <c r="AA90" s="2"/>
+      <c r="AB90" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="16">
+    <row r="91" spans="1:28" ht="16">
       <c r="A91" s="2" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>185</v>
@@ -10570,59 +10666,60 @@
       <c r="I91" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="2"/>
+      <c r="K91" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="K91" s="2" t="s">
+      <c r="L91" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N91" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L91" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M91" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N91" s="2" t="s">
+      <c r="O91" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="O91" s="2" t="s">
+      <c r="P91" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P91" s="2" t="s">
+      <c r="Q91" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Q91" s="2" t="s">
+      <c r="R91" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="R91" s="2">
+      <c r="S91" s="6">
         <v>2</v>
       </c>
-      <c r="S91" s="2" t="s">
+      <c r="T91" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="T91" s="2" t="s">
+      <c r="U91" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U91" s="2" t="s">
+      <c r="V91" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="V91" s="2" t="s">
+      <c r="W91" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="Z91" s="2"/>
-      <c r="AA91" s="2" t="s">
+      <c r="AA91" s="2"/>
+      <c r="AB91" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="92" spans="1:27">
+    <row r="92" spans="1:28">
       <c r="A92" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>170</v>
@@ -10636,59 +10733,60 @@
       <c r="I92" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="J92" s="4">
+      <c r="J92" s="2"/>
+      <c r="K92" s="6">
         <v>40000</v>
       </c>
-      <c r="K92" s="2" t="s">
+      <c r="L92" s="6">
+        <v>450000</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="N92" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L92" s="4">
-        <v>450000</v>
-      </c>
-      <c r="M92" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="N92" s="2" t="s">
+      <c r="O92" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="O92" s="2" t="s">
+      <c r="P92" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P92" s="2" t="s">
+      <c r="Q92" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="Q92" s="2" t="s">
+      <c r="R92" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R92" s="2">
+      <c r="S92" s="6">
         <v>3</v>
       </c>
-      <c r="S92" s="2" t="s">
+      <c r="T92" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="T92" s="2" t="s">
+      <c r="U92" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U92" s="2" t="s">
+      <c r="V92" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="V92" s="2" t="s">
+      <c r="W92" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="Z92" s="2"/>
-      <c r="AA92" s="2" t="s">
+      <c r="AA92" s="2"/>
+      <c r="AB92" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="32">
+    <row r="93" spans="1:28" ht="32">
       <c r="A93" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>159</v>
@@ -10702,59 +10800,60 @@
       <c r="I93" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="2"/>
+      <c r="K93" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K93" s="2" t="s">
+      <c r="L93" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="N93" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L93" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="M93" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N93" s="2" t="s">
+      <c r="O93" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O93" s="2" t="s">
+      <c r="P93" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="P93" s="2" t="s">
+      <c r="Q93" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="Q93" s="2" t="s">
+      <c r="R93" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R93" s="2">
+      <c r="S93" s="6">
         <v>3</v>
       </c>
-      <c r="S93" s="2" t="s">
+      <c r="T93" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="T93" s="2" t="s">
+      <c r="U93" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U93" s="2" t="s">
+      <c r="V93" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="V93" s="2" t="s">
+      <c r="W93" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="Z93" s="2"/>
-      <c r="AA93" s="2" t="s">
+      <c r="AA93" s="2"/>
+      <c r="AB93" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="94" spans="1:27">
+    <row r="94" spans="1:28">
       <c r="A94" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>145</v>
@@ -10768,59 +10867,60 @@
       <c r="I94" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J94" s="4">
+      <c r="J94" s="2"/>
+      <c r="K94" s="6">
         <v>10000</v>
       </c>
-      <c r="K94" s="2" t="s">
+      <c r="L94" s="6">
+        <v>80000</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="N94" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L94" s="4">
-        <v>80000</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="N94" s="2" t="s">
+      <c r="O94" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O94" s="2" t="s">
+      <c r="P94" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="P94" s="2" t="s">
+      <c r="Q94" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="Q94" s="2" t="s">
+      <c r="R94" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="R94" s="2">
+      <c r="S94" s="6">
         <v>4</v>
       </c>
-      <c r="S94" s="2" t="s">
+      <c r="T94" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="T94" s="2" t="s">
+      <c r="U94" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U94" s="2" t="s">
+      <c r="V94" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="V94" s="2" t="s">
+      <c r="W94" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="Z94" s="2"/>
-      <c r="AA94" s="2" t="s">
+      <c r="AA94" s="2"/>
+      <c r="AB94" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="16">
+    <row r="95" spans="1:28" ht="16">
       <c r="A95" s="2" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>134</v>
@@ -10834,59 +10934,60 @@
       <c r="I95" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="J95" s="3" t="s">
+      <c r="J95" s="2"/>
+      <c r="K95" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K95" s="2" t="s">
+      <c r="L95" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N95" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L95" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="N95" s="2" t="s">
+      <c r="O95" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="O95" s="2" t="s">
+      <c r="P95" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="P95" s="2" t="s">
+      <c r="Q95" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Q95" s="2" t="s">
+      <c r="R95" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="R95" s="2">
+      <c r="S95" s="6">
         <v>2</v>
       </c>
-      <c r="S95" s="2" t="s">
+      <c r="T95" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="T95" s="2" t="s">
+      <c r="U95" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U95" s="2" t="s">
+      <c r="V95" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="V95" s="2" t="s">
+      <c r="W95" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="Z95" s="2"/>
-      <c r="AA95" s="2" t="s">
+      <c r="AA95" s="2"/>
+      <c r="AB95" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="16">
+    <row r="96" spans="1:28" ht="16">
       <c r="A96" s="2" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>119</v>
@@ -10900,59 +11001,60 @@
       <c r="I96" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="2"/>
+      <c r="K96" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="K96" s="2" t="s">
+      <c r="L96" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="N96" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L96" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="N96" s="2" t="s">
+      <c r="O96" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="O96" s="2" t="s">
+      <c r="P96" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="P96" s="2" t="s">
+      <c r="Q96" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="Q96" s="2" t="s">
+      <c r="R96" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="R96" s="2">
+      <c r="S96" s="6">
         <v>2</v>
       </c>
-      <c r="S96" s="2" t="s">
+      <c r="T96" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="T96" s="2" t="s">
+      <c r="U96" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U96" s="2" t="s">
+      <c r="V96" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V96" s="2" t="s">
+      <c r="W96" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="Z96" s="2"/>
-      <c r="AA96" s="2" t="s">
+      <c r="AA96" s="2"/>
+      <c r="AB96" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="97" spans="1:27">
+    <row r="97" spans="1:28">
       <c r="A97" s="2" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>104</v>
@@ -10966,59 +11068,60 @@
       <c r="I97" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J97" s="4">
+      <c r="J97" s="2"/>
+      <c r="K97" s="6">
         <v>45000</v>
       </c>
-      <c r="K97" s="2" t="s">
+      <c r="L97" s="6">
+        <v>350000</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N97" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L97" s="4">
-        <v>350000</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="N97" s="2" t="s">
+      <c r="O97" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O97" s="2" t="s">
+      <c r="P97" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P97" s="2" t="s">
+      <c r="Q97" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="Q97" s="2" t="s">
+      <c r="R97" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="R97" s="2">
+      <c r="S97" s="6">
         <v>5</v>
       </c>
-      <c r="S97" s="2" t="s">
+      <c r="T97" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="T97" s="2" t="s">
+      <c r="U97" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U97" s="2" t="s">
+      <c r="V97" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="V97" s="2" t="s">
+      <c r="W97" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Z97" s="2"/>
-      <c r="AA97" s="2" t="s">
+      <c r="AA97" s="2"/>
+      <c r="AB97" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="16">
+    <row r="98" spans="1:28" ht="16">
       <c r="A98" s="2" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>88</v>
@@ -11032,59 +11135,60 @@
       <c r="I98" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J98" s="4">
+      <c r="J98" s="2"/>
+      <c r="K98" s="6">
         <v>30000</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="L98" s="6">
+        <v>350000</v>
+      </c>
+      <c r="M98" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N98" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L98" s="4">
-        <v>350000</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N98" s="2" t="s">
+      <c r="O98" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O98" s="2" t="s">
+      <c r="P98" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P98" s="2" t="s">
+      <c r="Q98" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Q98" s="2" t="s">
+      <c r="R98" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R98" s="2">
+      <c r="S98" s="6">
         <v>2</v>
       </c>
-      <c r="S98" s="2" t="s">
+      <c r="T98" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="T98" s="2" t="s">
+      <c r="U98" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U98" s="2" t="s">
+      <c r="V98" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V98" s="2" t="s">
+      <c r="W98" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="Z98" s="2"/>
-      <c r="AA98" s="2" t="s">
+      <c r="AA98" s="2"/>
+      <c r="AB98" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="16">
+    <row r="99" spans="1:28" ht="16">
       <c r="A99" s="2" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>75</v>
@@ -11098,59 +11202,60 @@
       <c r="I99" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="2"/>
+      <c r="K99" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="K99" s="2" t="s">
+      <c r="L99" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="N99" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L99" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N99" s="2" t="s">
+      <c r="O99" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="O99" s="2" t="s">
+      <c r="P99" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P99" s="2" t="s">
+      <c r="Q99" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q99" s="2" t="s">
+      <c r="R99" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="R99" s="2">
+      <c r="S99" s="6">
         <v>1</v>
       </c>
-      <c r="S99" s="2" t="s">
+      <c r="T99" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="T99" s="2" t="s">
+      <c r="U99" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U99" s="2" t="s">
+      <c r="V99" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="V99" s="2" t="s">
+      <c r="W99" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z99" s="2"/>
-      <c r="AA99" s="2" t="s">
+      <c r="AA99" s="2"/>
+      <c r="AB99" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="16">
+    <row r="100" spans="1:28" ht="16">
       <c r="A100" s="2" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>58</v>
@@ -11164,59 +11269,60 @@
       <c r="I100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="2"/>
+      <c r="K100" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K100" s="2" t="s">
+      <c r="L100" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N100" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L100" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N100" s="2" t="s">
+      <c r="O100" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O100" s="2" t="s">
+      <c r="P100" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P100" s="2" t="s">
+      <c r="Q100" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="Q100" s="2" t="s">
+      <c r="R100" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R100" s="2">
+      <c r="S100" s="6">
         <v>2</v>
       </c>
-      <c r="S100" s="2" t="s">
+      <c r="T100" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="T100" s="2" t="s">
+      <c r="U100" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U100" s="2" t="s">
+      <c r="V100" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V100" s="2" t="s">
+      <c r="W100" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Z100" s="2"/>
-      <c r="AA100" s="2" t="s">
+      <c r="AA100" s="2"/>
+      <c r="AB100" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="16">
+    <row r="101" spans="1:28" ht="16">
       <c r="A101" s="2" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>42</v>
@@ -11230,58 +11336,59 @@
       <c r="I101" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="2"/>
+      <c r="K101" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K101" s="2" t="s">
+      <c r="L101" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N101" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L101" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M101" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N101" s="2" t="s">
+      <c r="O101" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O101" s="2" t="s">
+      <c r="P101" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P101" s="2" t="s">
+      <c r="Q101" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q101" s="2" t="s">
+      <c r="R101" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="R101" s="2">
+      <c r="S101" s="6">
         <v>3</v>
       </c>
-      <c r="S101" s="2" t="s">
+      <c r="T101" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="T101" s="2" t="s">
+      <c r="U101" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="U101" s="2" t="s">
+      <c r="V101" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V101" s="2" t="s">
+      <c r="W101" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Z101" s="2"/>
-      <c r="AA101" s="2" t="s">
+      <c r="AA101" s="2"/>
+      <c r="AB101" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:27">
-      <c r="Z102" s="2"/>
-      <c r="AA102" s="2" t="s">
+    <row r="102" spans="1:28">
+      <c r="AA102" s="2"/>
+      <c r="AB102" s="2" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A2:A101">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
@@ -11291,5 +11398,38 @@
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2779D2A4-BC75-8241-B347-981DDEFA3134}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>D1:D1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4835AC-521B-B14F-9213-440E3B8BF035}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/apps/api/data/excel_templates/cities.xlsx
+++ b/apps/api/data/excel_templates/cities.xlsx
@@ -16029,7 +16029,7 @@
       <c r="Z186" s="10" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:Z1"/>
   <conditionalFormatting sqref="A2:A101">
     <cfRule type="duplicateValues" priority="6" dxfId="2"/>

--- a/apps/api/data/excel_templates/cities.xlsx
+++ b/apps/api/data/excel_templates/cities.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
     <col width="18" customWidth="1" style="4" min="24" max="24"/>
     <col width="18" customWidth="1" style="4" min="25" max="25"/>
     <col width="18" customWidth="1" style="1" min="26" max="26"/>
+    <col width="19" customWidth="1" style="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,6 +599,11 @@
       <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>metadata</t>
+        </is>
+      </c>
+      <c r="AA1" s="6" t="inlineStr">
+        <is>
+          <t>main_industries</t>
         </is>
       </c>
     </row>

--- a/apps/api/data/excel_templates/cities.xlsx
+++ b/apps/api/data/excel_templates/cities.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -608,7 +608,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:Z1"/>
   <dataValidations count="10">
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE." type="list">

--- a/apps/api/data/excel_templates/cities.xlsx
+++ b/apps/api/data/excel_templates/cities.xlsx
@@ -15521,7 +15521,7 @@
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$B$2:$B$155</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">

--- a/apps/api/data/excel_templates/cities.xlsx
+++ b/apps/api/data/excel_templates/cities.xlsx
@@ -6068,6 +6068,11 @@
           <t>EG</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>5.2 million (Foreign Born: 300,000)</t>
@@ -6167,6 +6172,11 @@
           <t>RO</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Teleorman</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>300,000 (Foreign Born: 8,000)</t>
@@ -6264,6 +6274,11 @@
       <c r="C59" t="inlineStr">
         <is>
           <t>US</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
